--- a/方块 block/beacon.xlsx
+++ b/方块 block/beacon.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\tree-hole\方块 block\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813E7216-34F2-44D6-A0E1-6C5FBF56168C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4212FB6C-9646-4D8A-990C-FA54DCC68D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2390" yWindow="1340" windowWidth="19200" windowHeight="11390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>效果倒计时</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -85,10 +85,6 @@
   </si>
   <si>
     <t>13/4=3.25x</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>w</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -521,9 +517,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G70"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.88671875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -537,13 +541,13 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>340</v>
       </c>
@@ -559,12 +563,12 @@
         <v/>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>335</v>
       </c>
       <c r="B3" t="str">
-        <f t="shared" ref="B3:B66" si="0">IF(MOD(340-A3,80)=0,"□","")</f>
+        <f t="shared" ref="B3:B65" si="0">IF(MOD(340-A3,80)=0,"□","")</f>
         <v/>
       </c>
       <c r="C3" s="1" t="str">
@@ -576,7 +580,7 @@
         <v/>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>330</v>
       </c>
@@ -593,7 +597,7 @@
         <v/>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>325</v>
       </c>
@@ -610,7 +614,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>320</v>
       </c>
@@ -627,7 +631,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>315</v>
       </c>
@@ -644,7 +648,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>310</v>
       </c>
@@ -661,7 +665,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>305</v>
       </c>
@@ -678,7 +682,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>300</v>
       </c>
@@ -695,7 +699,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>295</v>
       </c>
@@ -712,7 +716,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>290</v>
       </c>
@@ -729,7 +733,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>285</v>
       </c>
@@ -746,7 +750,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>280</v>
       </c>
@@ -763,7 +767,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>275</v>
       </c>
@@ -780,7 +784,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>270</v>
       </c>
@@ -797,7 +801,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>265</v>
       </c>
@@ -814,7 +818,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>260</v>
       </c>
@@ -836,7 +840,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>255</v>
       </c>
@@ -853,7 +857,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>250</v>
       </c>
@@ -870,7 +874,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>245</v>
       </c>
@@ -887,7 +891,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>240</v>
       </c>
@@ -904,7 +908,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>235</v>
       </c>
@@ -921,7 +925,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>230</v>
       </c>
@@ -938,7 +942,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>225</v>
       </c>
@@ -955,7 +959,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>220</v>
       </c>
@@ -972,7 +976,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>215</v>
       </c>
@@ -989,7 +993,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>210</v>
       </c>
@@ -1006,7 +1010,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>205</v>
       </c>
@@ -1023,7 +1027,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>200</v>
       </c>
@@ -1040,7 +1044,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>195</v>
       </c>
@@ -1057,7 +1061,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>190</v>
       </c>
@@ -1074,7 +1078,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>185</v>
       </c>
@@ -1091,7 +1095,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>180</v>
       </c>
@@ -1113,7 +1117,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>175</v>
       </c>
@@ -1130,7 +1134,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>170</v>
       </c>
@@ -1147,7 +1151,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>165</v>
       </c>
@@ -1164,7 +1168,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>160</v>
       </c>
@@ -1181,7 +1185,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>155</v>
       </c>
@@ -1198,7 +1202,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>150</v>
       </c>
@@ -1215,7 +1219,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>145</v>
       </c>
@@ -1232,7 +1236,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>140</v>
       </c>
@@ -1249,7 +1253,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>135</v>
       </c>
@@ -1266,7 +1270,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>130</v>
       </c>
@@ -1283,7 +1287,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>125</v>
       </c>
@@ -1300,7 +1304,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>120</v>
       </c>
@@ -1317,7 +1321,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>115</v>
       </c>
@@ -1334,7 +1338,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>110</v>
       </c>
@@ -1351,7 +1355,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>105</v>
       </c>
@@ -1368,7 +1372,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="6">
         <v>100</v>
       </c>
@@ -1390,10 +1394,10 @@
         <v>10</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>95</v>
       </c>
@@ -1410,16 +1414,16 @@
         <v/>
       </c>
       <c r="E51" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F51" s="6" t="s">
+      <c r="G51" t="s">
         <v>14</v>
       </c>
-      <c r="G51" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>90</v>
       </c>
@@ -1436,7 +1440,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>85</v>
       </c>
@@ -1453,7 +1457,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>80</v>
       </c>
@@ -1470,7 +1474,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>75</v>
       </c>
@@ -1487,7 +1491,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>70</v>
       </c>
@@ -1504,7 +1508,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>65</v>
       </c>
@@ -1521,7 +1525,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>60</v>
       </c>
@@ -1538,7 +1542,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>55</v>
       </c>
@@ -1555,7 +1559,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>50</v>
       </c>
@@ -1572,7 +1576,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>45</v>
       </c>
@@ -1589,7 +1593,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>40</v>
       </c>
@@ -1606,7 +1610,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>35</v>
       </c>
@@ -1623,7 +1627,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>30</v>
       </c>
@@ -1640,7 +1644,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>25</v>
       </c>
@@ -1657,7 +1661,7 @@
         <v>❤</v>
       </c>
     </row>
-    <row r="66" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="6">
         <v>20</v>
       </c>
@@ -1679,7 +1683,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>15</v>
       </c>
@@ -1696,7 +1700,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>10</v>
       </c>
@@ -1713,7 +1717,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>5</v>
       </c>
@@ -1730,7 +1734,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>0</v>
       </c>
